--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104495_W5.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104495_W5.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3757</v>
+        <v>4.5146</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0122</v>
+        <v>3.8319</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3635</v>
+        <v>0.6827</v>
       </c>
       <c r="G2" t="n">
-        <v>7.019</v>
+        <v>7.0141</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7346</v>
+        <v>4.7196</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2844</v>
+        <v>2.2945</v>
       </c>
       <c r="J2" t="n">
-        <v>6.6847</v>
+        <v>6.6514</v>
       </c>
       <c r="K2" t="n">
-        <v>4.8935</v>
+        <v>4.864</v>
       </c>
       <c r="L2" t="n">
-        <v>1.7912</v>
+        <v>1.7874</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3343</v>
+        <v>0.3627</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.159</v>
+        <v>-0.1444</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4932</v>
+        <v>0.5071</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5622</v>
+        <v>-0.4005</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2571</v>
+        <v>-0.3743</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3052</v>
+        <v>-0.0262</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1212</v>
+        <v>2.1075</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1191</v>
+        <v>1.6307</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4383</v>
+        <v>0.9463</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6807</v>
+        <v>0.6844</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7323</v>
+        <v>4.756</v>
       </c>
       <c r="H3" t="n">
-        <v>0.574</v>
+        <v>0.5907</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1583</v>
+        <v>4.1653</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7848</v>
+        <v>3.7761</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2771</v>
+        <v>0.2758</v>
       </c>
       <c r="L3" t="n">
-        <v>3.5078</v>
+        <v>3.5003</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9475</v>
+        <v>0.98</v>
       </c>
       <c r="N3" t="n">
-        <v>0.297</v>
+        <v>0.3149</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6505</v>
+        <v>0.665</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3602</v>
+        <v>-0.1449</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8953</v>
+        <v>0.427</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5351</v>
+        <v>-0.5719</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. AKOBUNDU</t>
+          <t>A. REYES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9437</v>
+        <v>1.28</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9181</v>
+        <v>-1.534</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9744</v>
+        <v>2.814</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5386</v>
+        <v>-0.4206</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3679</v>
+        <v>0.491</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1707</v>
+        <v>-0.9116</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1797</v>
+        <v>-1.4583</v>
       </c>
       <c r="K4" t="n">
-        <v>3.0304</v>
+        <v>-0.3555</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1493</v>
+        <v>-1.1029</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6411</v>
+        <v>1.0377</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6626</v>
+        <v>0.8465</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0214</v>
+        <v>0.1912</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8154</v>
+        <v>-0.1612</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8953</v>
+        <v>-0.5718</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0799</v>
+        <v>0.4105</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.8639</v>
+        <v>1.6342</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.1568</v>
+        <v>1.6342</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. REYES</t>
+          <t>K. AKOBUNDU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0311</v>
+        <v>0.8254</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.9721</v>
+        <v>1.9577</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0032</v>
+        <v>-1.1323</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4225</v>
+        <v>2.5516</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4891</v>
+        <v>2.3694</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9116</v>
+        <v>0.1822</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.4335</v>
+        <v>3.1654</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3432</v>
+        <v>3.0164</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.0903</v>
+        <v>0.1489</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0111</v>
+        <v>-0.6138</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8324</v>
+        <v>-0.6471</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1787</v>
+        <v>0.0333</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4122</v>
+        <v>-0.3181</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0434</v>
+        <v>-0.0468</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6312</v>
+        <v>-0.2713</v>
       </c>
       <c r="V5" t="n">
-        <v>1.639</v>
+        <v>-1.8634</v>
       </c>
       <c r="W5" t="n">
-        <v>1.639</v>
+        <v>-1.1609</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5697</v>
+        <v>0.5805</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2281</v>
+        <v>-0.2431</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7978</v>
+        <v>0.8236</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6937</v>
+        <v>0.7058</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.13</v>
+        <v>-0.1211</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8237</v>
+        <v>0.8269</v>
       </c>
       <c r="J6" t="n">
-        <v>0.509</v>
+        <v>0.5026</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1385</v>
+        <v>0.1379</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3705</v>
+        <v>0.3647</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1847</v>
+        <v>0.2032</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2685</v>
+        <v>-0.259</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.124</v>
+        <v>-0.1253</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6956</v>
+        <v>-0.697</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5716</v>
+        <v>0.5718</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2979</v>
+        <v>0.4313</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2263</v>
+        <v>0.2231</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0716</v>
+        <v>0.2082</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1287</v>
+        <v>1.1323</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8355</v>
+        <v>0.8358</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2932</v>
+        <v>0.2966</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.5716</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5343</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5546</v>
+        <v>0.5608</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2986</v>
+        <v>0.3014</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7361</v>
+        <v>-0.6132</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3478</v>
+        <v>-0.3485</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3883</v>
+        <v>-0.2647</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="8">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1808</v>
+        <v>0.2447</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1098</v>
+        <v>0.098</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0711</v>
+        <v>0.1467</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5302</v>
+        <v>-0.5239</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4502</v>
+        <v>-0.4482</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0799</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1603</v>
+        <v>-0.1664</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1976</v>
+        <v>-0.2036</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3699</v>
+        <v>-0.3576</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.291</v>
+        <v>-0.2298</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0514</v>
+        <v>-0.0512</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2395</v>
+        <v>-0.1786</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5551</v>
+        <v>-1.0483</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1173</v>
+        <v>-3.5165</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5622</v>
+        <v>2.4682</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3705</v>
+        <v>2.3777</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3709</v>
+        <v>1.3673</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9997</v>
+        <v>1.0104</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8499</v>
+        <v>0.8254</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5616</v>
+        <v>1.5406</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>1.5206</v>
+        <v>1.5523</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1908</v>
+        <v>-0.1733</v>
       </c>
       <c r="O9" t="n">
-        <v>1.7114</v>
+        <v>1.7256</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.1757</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.5547</v>
       </c>
       <c r="T9" t="n">
-        <v>0.248</v>
+        <v>-0.1048</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3194</v>
+        <v>-0.4499</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. GOLDEN</t>
+          <t>R. OBASOHAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6943</v>
+        <v>-2.1981</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.656</v>
+        <v>-3.976</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9617</v>
+        <v>1.7779</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0016</v>
+        <v>-2.9218</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5134</v>
+        <v>-1.4875</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5118</v>
+        <v>-1.4343</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.9057</v>
+        <v>-3.5714</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9057</v>
+        <v>-1.3142</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-2.2572</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9042</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3923</v>
+        <v>-0.1733</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5118</v>
+        <v>0.8229</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6021</v>
+        <v>-0.8697</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3478</v>
+        <v>-0.4046</v>
       </c>
       <c r="U10" t="n">
-        <v>0.95</v>
+        <v>-0.4651</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. PEREZ</t>
+          <t>G. GOLDEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0704</v>
+        <v>-2.5764</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6113</v>
+        <v>-5.2207</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4591</v>
+        <v>2.6443</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9324</v>
+        <v>-1.0112</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7591</v>
+        <v>-1.5299</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1733</v>
+        <v>0.5187</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1209</v>
+        <v>-1.9315</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7131</v>
+        <v>-1.9315</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4078</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1885</v>
+        <v>0.9203</v>
       </c>
       <c r="N11" t="n">
-        <v>0.046</v>
+        <v>0.4016</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2345</v>
+        <v>0.5187</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.4952</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0935</v>
+        <v>0.7308</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3297</v>
+        <v>0.1253</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2362</v>
+        <v>0.6055</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4141</v>
+        <v>-0.7025</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4141</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. OBASOHAN</t>
+          <t>D. PEREZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3778</v>
+        <v>-2.8697</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.6526</v>
+        <v>-2.4097</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2748</v>
+        <v>-0.46</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.9226</v>
+        <v>0.9287</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4833</v>
+        <v>0.7528</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.4393</v>
+        <v>0.1759</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.5397</v>
+        <v>1.0979</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2925</v>
+        <v>0.696</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.2471</v>
+        <v>0.4019</v>
       </c>
       <c r="M12" t="n">
-        <v>0.617</v>
+        <v>-0.1692</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1908</v>
+        <v>0.0568</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8078</v>
+        <v>-0.226</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5878</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.043</v>
+        <v>0.1105</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.113</v>
+        <v>-0.0931</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.93</v>
+        <v>0.2036</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.405</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8203999999999998</v>
+        <v>0.8146999999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.5327</v>
+        <v>-9.843</v>
       </c>
       <c r="F13" t="n">
-        <v>10.3531</v>
+        <v>10.6577</v>
       </c>
       <c r="G13" t="n">
-        <v>14.5383</v>
+        <v>14.5887</v>
       </c>
       <c r="H13" t="n">
-        <v>7.554200000000002</v>
+        <v>7.5399</v>
       </c>
       <c r="I13" t="n">
-        <v>6.984299999999998</v>
+        <v>7.048800000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>9.663900000000002</v>
+        <v>9.462800000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>7.412000000000003</v>
+        <v>7.260199999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>2.252099999999999</v>
+        <v>2.202300000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>4.8745</v>
+        <v>5.1261</v>
       </c>
       <c r="N13" t="n">
-        <v>0.142</v>
+        <v>0.2795</v>
       </c>
       <c r="O13" t="n">
-        <v>4.7322</v>
+        <v>4.8463</v>
       </c>
       <c r="P13" t="n">
-        <v>-9.073399999999999</v>
+        <v>-9.1052</v>
       </c>
       <c r="Q13" t="n">
-        <v>-21.5493</v>
+        <v>-21.6251</v>
       </c>
       <c r="R13" t="n">
-        <v>12.4758</v>
+        <v>12.5198</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.5557</v>
+        <v>-2.5761</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.1472</v>
+        <v>-2.1398</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4084000000000001</v>
+        <v>-0.4363</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.0889</v>
+        <v>-2.0926</v>
       </c>
       <c r="W13" t="n">
-        <v>4.4996</v>
+        <v>4.459099999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.5885</v>
+        <v>-6.5517</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3796</v>
+        <v>3.8097</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9847</v>
+        <v>3.2452</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3949</v>
+        <v>0.5645</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5492</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1028</v>
+        <v>2.0812</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3192</v>
+        <v>1.2993</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7837</v>
+        <v>0.782</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4643</v>
+        <v>-1.4335</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2298</v>
+        <v>-1.2075</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2854</v>
+        <v>1.7083</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2824</v>
+        <v>0.58</v>
       </c>
       <c r="U14" t="n">
-        <v>2.003</v>
+        <v>1.1283</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W14" t="n">
-        <v>1.9604</v>
+        <v>1.9497</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.739</v>
+        <v>2.7164</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9161</v>
+        <v>1.0065</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8229</v>
+        <v>1.7098</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1947</v>
+        <v>-0.1914</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.1588</v>
+        <v>-3.1511</v>
       </c>
       <c r="I15" t="n">
-        <v>2.964</v>
+        <v>2.9597</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7413</v>
+        <v>1.7159</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.6145</v>
+        <v>-1.6277</v>
       </c>
       <c r="L15" t="n">
-        <v>3.3558</v>
+        <v>3.3436</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9361</v>
+        <v>-1.9073</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5443</v>
+        <v>-1.5233</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S15" t="n">
-        <v>1.119</v>
+        <v>1.0867</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3751</v>
+        <v>0.4986</v>
       </c>
       <c r="U15" t="n">
-        <v>0.744</v>
+        <v>0.5881</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. LAZAREVIC</t>
+          <t>L. PETRASEK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4882</v>
+        <v>2.3355</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0553</v>
+        <v>1.266</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4329</v>
+        <v>1.0695</v>
       </c>
       <c r="G16" t="n">
-        <v>0.06</v>
+        <v>-1.5122</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8729</v>
+        <v>-0.7957</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8129999999999999</v>
+        <v>-0.7165</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2216</v>
+        <v>0.1098</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8587</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6371</v>
+        <v>-0.6035</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1617</v>
+        <v>-1.6219</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0142</v>
+        <v>-1.5089</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1759</v>
+        <v>-0.113</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>2.7316</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0415</v>
+        <v>2.7316</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5228</v>
+        <v>0.1844</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1947</v>
+        <v>0.0668</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3281</v>
+        <v>0.1176</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2249</v>
+        <v>0.9317</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>0.2249</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. PETRASEK</t>
+          <t>S. LAZAREVIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.936</v>
+        <v>2.1121</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9330000000000001</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>1.003</v>
+        <v>2.7789</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.515</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.798</v>
+        <v>0.8758</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.717</v>
+        <v>-0.8102</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1306</v>
+        <v>0.2072</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7304</v>
+        <v>0.8479</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5998</v>
+        <v>-0.6407</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6457</v>
+        <v>-0.1416</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5284</v>
+        <v>0.028</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1172</v>
+        <v>-0.1695</v>
       </c>
       <c r="P17" t="n">
-        <v>2.722</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>2.722</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2029</v>
+        <v>1.1344</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2903</v>
+        <v>0.4918</v>
       </c>
       <c r="U17" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.2292</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2209</v>
+        <v>-0.0963</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6969</v>
+        <v>-1.183</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9177999999999999</v>
+        <v>1.0867</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1317</v>
+        <v>0.1303</v>
       </c>
       <c r="H18" t="n">
-        <v>0.153</v>
+        <v>0.1495</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0213</v>
+        <v>-0.0193</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0648</v>
+        <v>0.0577</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0275</v>
+        <v>0.0205</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0669</v>
+        <v>0.0725</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1255</v>
+        <v>0.129</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5429</v>
+        <v>0.2287</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4386</v>
+        <v>-0.0327</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1043</v>
+        <v>0.2614</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3801</v>
+        <v>-0.1133</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9323</v>
+        <v>-0.7199</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5521</v>
+        <v>0.6066</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.0992</v>
+        <v>-2.1069</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0302</v>
+        <v>1.0338</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.1294</v>
+        <v>-3.1406</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.9452</v>
+        <v>-1.9637</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1256</v>
+        <v>1.1204</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.0708</v>
+        <v>-3.0841</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.154</v>
+        <v>-0.1432</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5719</v>
+        <v>-0.3055</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6261</v>
+        <v>-0.3904</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0541</v>
+        <v>0.0849</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1568</v>
+        <v>1.1609</v>
       </c>
       <c r="W19" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.4822</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. BAGAYOKO</t>
+          <t>M. NORMANTAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9999</v>
+        <v>-1.209</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6285</v>
+        <v>-2.9565</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6286</v>
+        <v>1.7475</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7761</v>
+        <v>-0.8724</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6349</v>
+        <v>-2.068</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1413</v>
+        <v>1.1955</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4808</v>
+        <v>-1.1886</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.5554</v>
+        <v>-2.2827</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0746</v>
+        <v>1.0941</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2954</v>
+        <v>0.3162</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0795</v>
+        <v>0.2148</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2159</v>
+        <v>0.1014</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6155</v>
+        <v>-0.3578</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8257</v>
+        <v>-0.581</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2102</v>
+        <v>0.2232</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1607</v>
+        <v>0.9317</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. NORMANTAS</t>
+          <t>B. BAGAYOKO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5846</v>
+        <v>-1.5505</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1533</v>
+        <v>-2.3476</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5687</v>
+        <v>0.797</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8592</v>
+        <v>-1.7742</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.0692</v>
+        <v>-1.6342</v>
       </c>
       <c r="I21" t="n">
-        <v>1.21</v>
+        <v>-0.14</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1611</v>
+        <v>-1.4876</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.2725</v>
+        <v>-1.562</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1114</v>
+        <v>0.0745</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3019</v>
+        <v>-0.2866</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2033</v>
+        <v>-0.0722</v>
       </c>
       <c r="O21" t="n">
-        <v>0.09859999999999999</v>
+        <v>-0.2144</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9073</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7501</v>
+        <v>0.0659</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8166</v>
+        <v>0.1204</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0665</v>
+        <v>-0.0545</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.1578</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1528</v>
+        <v>-1.5659</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3255</v>
+        <v>-0.9747</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8273</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8167</v>
+        <v>-0.8157</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0304</v>
+        <v>-0.0261</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.769</v>
+        <v>-0.7724</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0477</v>
+        <v>-0.0433</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0477</v>
+        <v>-0.0433</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8293</v>
+        <v>-0.2557</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5565</v>
+        <v>-0.2023</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2728</v>
+        <v>-0.0534</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4826</v>
+        <v>-1.7927</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3803</v>
+        <v>-3.1345</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8977000000000001</v>
+        <v>1.3418</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.8809</v>
+        <v>-3.9048</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4098</v>
+        <v>-1.4102</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.4711</v>
+        <v>-2.4947</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.9607</v>
+        <v>-2.0119</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0386</v>
+        <v>-0.0592</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.9221</v>
+        <v>-1.9528</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.9202</v>
+        <v>-1.8929</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3711</v>
+        <v>-1.351</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P23" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R23" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4163</v>
+        <v>0.2911</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0585</v>
+        <v>0.2432</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3578</v>
+        <v>0.0479</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9842</v>
+        <v>-4.6711</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1256</v>
+        <v>-4.1926</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8586</v>
+        <v>-0.4786</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.2267</v>
+        <v>-4.2546</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5987</v>
+        <v>-0.6056</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.628</v>
+        <v>-3.649</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.8188</v>
+        <v>-1.8735</v>
       </c>
       <c r="K24" t="n">
-        <v>1.2601</v>
+        <v>1.2336</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.0789</v>
+        <v>-3.1071</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.4079</v>
+        <v>-2.3811</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.8588</v>
+        <v>-1.8392</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7594</v>
+        <v>-0.4149</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3599</v>
+        <v>-0.3583</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3995</v>
+        <v>-0.0567</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="W24" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.8205000000000018</v>
+        <v>-0.02510000000000012</v>
       </c>
       <c r="E25" t="n">
-        <v>-10.3533</v>
+        <v>-10.6579</v>
       </c>
       <c r="F25" t="n">
-        <v>9.532700000000002</v>
+        <v>10.6325</v>
       </c>
       <c r="G25" t="n">
-        <v>-14.5382</v>
+        <v>-14.5886</v>
       </c>
       <c r="H25" t="n">
-        <v>-7.5543</v>
+        <v>-7.539999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-6.984299999999999</v>
+        <v>-7.0488</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.874499999999999</v>
+        <v>-5.125900000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.1421999999999992</v>
+        <v>-0.2795000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>-4.7323</v>
+        <v>-4.846399999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-9.664199999999999</v>
+        <v>-9.4627</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.411999999999999</v>
+        <v>-7.260200000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.2519</v>
+        <v>-2.2023</v>
       </c>
       <c r="P25" t="n">
-        <v>9.073400000000001</v>
+        <v>9.105399999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>-12.4758</v>
+        <v>-12.5198</v>
       </c>
       <c r="R25" t="n">
-        <v>21.5493</v>
+        <v>21.6249</v>
       </c>
       <c r="S25" t="n">
-        <v>2.5557</v>
+        <v>3.3656</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4086000000000002</v>
+        <v>0.4361</v>
       </c>
       <c r="U25" t="n">
-        <v>2.147099999999999</v>
+        <v>2.9294</v>
       </c>
       <c r="V25" t="n">
-        <v>2.0888</v>
+        <v>2.0926</v>
       </c>
       <c r="W25" t="n">
-        <v>6.588299999999999</v>
+        <v>6.5518</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.4995</v>
+        <v>-4.4592</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104495_W5.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104495_W5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104495_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104495_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104495_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104495_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104495_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104495_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104495_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104495_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104495_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104495_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104495_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-6.5517</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104495_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104495_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104495_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104495_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104495_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104495_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104495_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104495_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104495_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104495_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104495_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-4.4592</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
